--- a/YENİŞEHİR.xlsx
+++ b/YENİŞEHİR.xlsx
@@ -458,7 +458,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>GGGG</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>1.Öncelik - İmar Planı Sahasında</v>
